--- a/inputs/templates/TEMPLATE_FONDO_ALTO_CAPITAL.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_ALTO_CAPITAL.xlsx
@@ -3213,11 +3213,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="25245866"/>
-        <c:axId val="83410742"/>
+        <c:axId val="78466274"/>
+        <c:axId val="17025246"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="25245866"/>
+        <c:axId val="78466274"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3251,7 +3251,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83410742"/>
+        <c:crossAx val="17025246"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3263,7 +3263,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="83410742"/>
+        <c:axId val="17025246"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3306,7 +3306,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25245866"/>
+        <c:crossAx val="78466274"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5232,11 +5232,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="32673921"/>
-        <c:axId val="38979380"/>
+        <c:axId val="2233003"/>
+        <c:axId val="95760892"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="32673921"/>
+        <c:axId val="2233003"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5268,7 +5268,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38979380"/>
+        <c:crossAx val="95760892"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5279,7 +5279,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="38979380"/>
+        <c:axId val="95760892"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5355,7 +5355,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32673921"/>
+        <c:crossAx val="2233003"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="AW20" s="33" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2973,$B$3:$B$2973)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="33" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2973,$B$3:$B$2973)</f>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AH22" s="23" t="n">
         <f aca="false">+(S23/R23-1)</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="10"/>
       <c r="AJ22" s="10"/>
@@ -9767,7 +9767,7 @@
       <c r="AP22" s="10"/>
       <c r="AQ22" s="24" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AR22" s="27"/>
       <c r="AS22" s="10"/>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="S23" s="4" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
@@ -10398,23 +10398,23 @@
       </c>
       <c r="AX29" s="43" t="n">
         <f aca="false">$AW20/AX20-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="43" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="43" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="43" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="43" t="n">
         <f aca="false">+AQ83</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="44"/>
       <c r="BD29" s="28"/>
@@ -15448,7 +15448,7 @@
       </c>
       <c r="AH83" s="50" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI83" s="50"/>
       <c r="AJ83" s="50"/>
@@ -15460,7 +15460,7 @@
       <c r="AP83" s="50"/>
       <c r="AQ83" s="50" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="84" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21923,15 +21923,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="4" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="26" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="4" t="n">
         <f aca="false">B249/$B$3*100</f>
-        <v>179.266768079531</v>
+        <v>181.836900088812</v>
       </c>
       <c r="F249" s="19" t="n">
         <v>46142</v>
@@ -22020,23 +22020,23 @@
       </c>
       <c r="T2" s="86" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="86" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="86" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="86" t="n">
         <f aca="false">+'Datos ICP (2)'!BA29</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="X2" s="86" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23785,7 +23785,7 @@
       </c>
       <c r="H37" s="102" t="n">
         <f aca="false">+'Datos ICP (2)'!AH83</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I37" s="105"/>
       <c r="J37" s="105"/>
@@ -23797,7 +23797,7 @@
       <c r="P37" s="105"/>
       <c r="Q37" s="105" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ83</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_ALTO_CAPITAL.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_ALTO_CAPITAL.xlsx
@@ -3213,11 +3213,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="78466274"/>
-        <c:axId val="17025246"/>
+        <c:axId val="47647917"/>
+        <c:axId val="33607680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="78466274"/>
+        <c:axId val="47647917"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3251,7 +3251,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17025246"/>
+        <c:crossAx val="33607680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3263,7 +3263,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="17025246"/>
+        <c:axId val="33607680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3306,7 +3306,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78466274"/>
+        <c:crossAx val="47647917"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5232,11 +5232,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="2233003"/>
-        <c:axId val="95760892"/>
+        <c:axId val="42591254"/>
+        <c:axId val="5255680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="2233003"/>
+        <c:axId val="42591254"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5268,7 +5268,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95760892"/>
+        <c:crossAx val="5255680"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5279,7 +5279,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="95760892"/>
+        <c:axId val="5255680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5355,7 +5355,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2233003"/>
+        <c:crossAx val="42591254"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_ALTO_CAPITAL.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_ALTO_CAPITAL.xlsx
@@ -3213,11 +3213,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="47647917"/>
-        <c:axId val="33607680"/>
+        <c:axId val="88659072"/>
+        <c:axId val="96304864"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="47647917"/>
+        <c:axId val="88659072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3251,7 +3251,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33607680"/>
+        <c:crossAx val="96304864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3263,7 +3263,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="33607680"/>
+        <c:axId val="96304864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3306,7 +3306,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47647917"/>
+        <c:crossAx val="88659072"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5232,11 +5232,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="42591254"/>
-        <c:axId val="5255680"/>
+        <c:axId val="68293273"/>
+        <c:axId val="42701956"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="42591254"/>
+        <c:axId val="68293273"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5268,7 +5268,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5255680"/>
+        <c:crossAx val="42701956"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5279,7 +5279,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="5255680"/>
+        <c:axId val="42701956"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5355,7 +5355,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42591254"/>
+        <c:crossAx val="68293273"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_ALTO_CAPITAL.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_ALTO_CAPITAL.xlsx
@@ -3213,11 +3213,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="88659072"/>
-        <c:axId val="96304864"/>
+        <c:axId val="91443773"/>
+        <c:axId val="5408422"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="88659072"/>
+        <c:axId val="91443773"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3251,7 +3251,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96304864"/>
+        <c:crossAx val="5408422"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3263,7 +3263,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="96304864"/>
+        <c:axId val="5408422"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3306,7 +3306,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88659072"/>
+        <c:crossAx val="91443773"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5232,11 +5232,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="68293273"/>
-        <c:axId val="42701956"/>
+        <c:axId val="81012660"/>
+        <c:axId val="49490188"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="68293273"/>
+        <c:axId val="81012660"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5268,7 +5268,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42701956"/>
+        <c:crossAx val="49490188"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5279,7 +5279,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="42701956"/>
+        <c:axId val="49490188"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5355,7 +5355,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68293273"/>
+        <c:crossAx val="81012660"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
